--- a/results/Dow_fire_and_explosion_index.xlsx
+++ b/results/Dow_fire_and_explosion_index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165E0D89-B0DB-4DF7-BA5A-D41511692148}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B0EC26-72F1-4A26-8F50-923C2F6DA995}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12030" xr2:uid="{5A6EAF40-D32D-45A0-96A8-57E2CE328A40}"/>
   </bookViews>
